--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/sep-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/sep-2026.xlsx
@@ -1172,7 +1172,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1237,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1363,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1428,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1676,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1741,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1806,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2054,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2119,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2184,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2249,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2375,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2562,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2627,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2997,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3184,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3676,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3741,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3867,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4115,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4180,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4245,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4493,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4619,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4684,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4871,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5241,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5672,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5859,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5924,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6050,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6481,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6912,11 @@
           <t>77.814.662-2</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7282,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7469,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7656,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7782,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7847,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +7973,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8282,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8347,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8534,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8599,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8664,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8851,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9038,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9103,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9412,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9538,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9725,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9790,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9916,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10042,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10107,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10172,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10237,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10424,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10733,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10798,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +10985,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11050,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11115,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11302,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11489,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12042,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12107,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12782,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12847,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +12973,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13160,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13225,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13412,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13477,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13542,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13729,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13794,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13859,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +13924,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14172,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14237,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14668,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15038,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15103,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15351,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15416,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15603,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15729,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15794,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16042,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16534,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16599,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +16969,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17095,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17221,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17347,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17534,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18026,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18152,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18400,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18587,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18652,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18717,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +18782,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +18908,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +18973,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19221,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19286,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19351,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19477,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19603,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/sep-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1078078-3413-CM26</t>
+          <t>1078078-3411-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8526,26 +8526,22 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>492.14</v>
+        <v>641.99</v>
       </c>
     </row>
     <row r="131">
@@ -8868,7 +8864,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1078078-3411-CM26</t>
+          <t>1078078-3413-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8908,22 +8904,26 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>641.99</v>
+        <v>492.14</v>
       </c>
     </row>
     <row r="137">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -10124,7 +10124,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>838104-847-CM26</t>
+          <t>1078078-3381-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10144,17 +10144,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10164,17 +10164,17 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10183,13 +10183,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>28.87</v>
+        <v>636.42</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1078078-3381-CM26</t>
+          <t>838104-847-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10209,17 +10209,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10229,17 +10229,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10248,7 +10248,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>636.42</v>
+        <v>28.87</v>
       </c>
     </row>
     <row r="158">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -14376,7 +14376,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1078078-3480-CM26</t>
+          <t>1078078-3481-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14431,7 +14431,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>437.74</v>
+        <v>7938.29</v>
       </c>
     </row>
     <row r="225">
@@ -14498,7 +14498,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1078078-3475-CM26</t>
+          <t>2674-807-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14518,17 +14518,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14538,28 +14538,32 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>158.66</v>
+        <v>23343.75</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1078078-3469-CM26</t>
+          <t>1078078-3480-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14599,12 +14603,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14614,13 +14618,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>217.43</v>
+        <v>437.74</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2674-807-CM26</t>
+          <t>1078078-3475-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14640,17 +14644,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14660,32 +14664,28 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>23343.75</v>
+        <v>158.66</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1078078-3481-CM26</t>
+          <t>1078078-3469-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14725,12 +14725,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.462.500-5</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>7938.29</v>
+        <v>217.43</v>
       </c>
     </row>
     <row r="230">
@@ -15368,7 +15368,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1078078-3496-CM26</t>
+          <t>1078078-3498-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15408,32 +15408,28 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1182.3</v>
+        <v>10710.83</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1078078-3494-CM26</t>
+          <t>1480133-123-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15458,12 +15454,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15473,28 +15469,32 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr"/>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>521.5599999999999</v>
+        <v>4943.92</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1078078-3493-CM26</t>
+          <t>1078078-3488-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15534,12 +15534,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15549,13 +15549,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>8179.12</v>
+        <v>914.5</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>4371-417-CM26</t>
+          <t>1480133-121-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15580,27 +15580,27 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -15614,13 +15614,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>334.28</v>
+        <v>3410.27</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1078078-3488-CM26</t>
+          <t>1078078-3493-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15660,12 +15660,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15675,13 +15675,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>914.5</v>
+        <v>8179.12</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1480133-123-CM26</t>
+          <t>1078078-3494-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15706,12 +15706,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15721,32 +15721,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>4943.92</v>
+        <v>521.5599999999999</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1480133-121-CM26</t>
+          <t>1078078-3496-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15771,12 +15767,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15786,17 +15782,17 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -15805,13 +15801,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>3410.27</v>
+        <v>1182.3</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1078078-3498-CM26</t>
+          <t>4371-417-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15831,48 +15827,52 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr"/>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>10710.83</v>
+        <v>334.28</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1078078-3521-CM26</t>
+          <t>1078078-3524-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15912,12 +15912,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15927,13 +15927,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>266.59</v>
+        <v>130.78</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1078078-3522-CM26</t>
+          <t>1078078-3520-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15973,12 +15973,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15988,13 +15988,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>573.23</v>
+        <v>6972.27</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2341-490-CM26</t>
+          <t>1078078-3523-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16019,12 +16019,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16034,32 +16034,28 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>16545.99</v>
+        <v>7529.72</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1078078-3524-CM26</t>
+          <t>5349-1928-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16079,32 +16075,32 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -16114,13 +16110,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>130.78</v>
+        <v>3566.07</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5349-1928-CM26</t>
+          <t>5349-1927-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16140,7 +16136,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -16181,7 +16177,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1078078-3523-CM26</t>
+          <t>2341-490-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16206,12 +16202,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16221,28 +16217,32 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr"/>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>7529.72</v>
+        <v>16545.99</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1078078-3520-CM26</t>
+          <t>1078078-3522-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16282,12 +16282,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -16297,13 +16297,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>6972.27</v>
+        <v>573.23</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5349-1927-CM26</t>
+          <t>1078078-3521-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16328,27 +16328,27 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3566.07</v>
+        <v>266.59</v>
       </c>
     </row>
     <row r="256">
@@ -16860,7 +16860,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1078078-3261-CM26</t>
+          <t>1078078-3518-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16900,28 +16900,32 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>supermercado mayorista metropolitano</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.047.926-6</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>111727.21</v>
+        <v>2408.08</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1078078-3518-CM26</t>
+          <t>1078078-3261-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16961,26 +16965,22 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.047.926-6</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2408.08</v>
+        <v>111727.21</v>
       </c>
     </row>
     <row r="266">
@@ -17047,7 +17047,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1078078-3530-CM26</t>
+          <t>1078078-3528-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17087,32 +17087,28 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>418.35</v>
+        <v>1307.01</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1078078-3528-CM26</t>
+          <t>1078078-3530-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17152,28 +17148,32 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1307.01</v>
+        <v>418.35</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1039-277-CM26</t>
+          <t>1078078-3526-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17193,17 +17193,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17213,32 +17213,28 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1477.78</v>
+        <v>140.46</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1078078-3526-CM26</t>
+          <t>1039-277-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17258,17 +17254,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17278,22 +17274,26 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>140.46</v>
+        <v>1477.78</v>
       </c>
     </row>
     <row r="271">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -17734,7 +17734,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1078078-3542-CM26</t>
+          <t>1078078-3539-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17774,28 +17774,32 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4935.64</v>
+        <v>580.64</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1078078-3538-CM26</t>
+          <t>1078078-3542-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17835,12 +17839,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
@@ -17850,7 +17854,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>7902.7</v>
+        <v>4935.64</v>
       </c>
     </row>
     <row r="280">
@@ -18104,7 +18108,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1078078-3539-CM26</t>
+          <t>1036-241-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18129,47 +18133,43 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>580.64</v>
+        <v>5615.13</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1078078-3557-CM26</t>
+          <t>1078078-3538-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -18209,12 +18209,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -18224,13 +18224,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>1184.36</v>
+        <v>7902.7</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1078078-3563-CM26</t>
+          <t>1078078-3557-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -18285,13 +18285,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>620.29</v>
+        <v>1184.36</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1078078-3562-CM26</t>
+          <t>1078078-3563-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18346,13 +18346,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>8028.87</v>
+        <v>620.29</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1078078-3561-CM26</t>
+          <t>1078078-3562-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18392,32 +18392,28 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>77.544.929-2</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>15680.23</v>
+        <v>8028.87</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1078078-3560-CM26</t>
+          <t>1078078-3561-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18457,28 +18453,32 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr"/>
+          <t>77.544.929-2</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>584.76</v>
+        <v>15680.23</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1078078-3559-CM26</t>
+          <t>1078078-3560-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18518,12 +18518,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>7793.46</v>
+        <v>584.76</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1078078-3564-CM26</t>
+          <t>1078078-3559-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18579,32 +18579,28 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>311.54</v>
+        <v>7793.46</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2408-980-CM26</t>
+          <t>1078078-3564-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18629,32 +18625,32 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -18663,13 +18659,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>7212.27</v>
+        <v>311.54</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1078078-3556-CM26</t>
+          <t>2408-980-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18694,27 +18690,27 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -18728,13 +18724,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>4763.08</v>
+        <v>7212.27</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1078078-3552-CM26</t>
+          <t>1078078-3556-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18774,17 +18770,17 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -18793,13 +18789,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>8460.540000000001</v>
+        <v>4763.08</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1078078-3554-CM26</t>
+          <t>1078078-3552-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18839,28 +18835,32 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>7422.35</v>
+        <v>8460.540000000001</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1078078-3553-CM26</t>
+          <t>1078078-3554-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18900,32 +18900,28 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>692.24</v>
+        <v>7422.35</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1078078-3551-CM26</t>
+          <t>1078078-3553-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18984,13 +18980,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>12706.67</v>
+        <v>692.24</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1078078-3550-CM26</t>
+          <t>1078078-3551-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19030,28 +19026,32 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>15586.79</v>
+        <v>12706.67</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1078078-3548-CM26</t>
+          <t>1078078-3550-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19106,13 +19106,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1780.08</v>
+        <v>15586.79</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1078078-3547-CM26</t>
+          <t>1078078-3548-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19152,12 +19152,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -19167,13 +19167,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>7841.73</v>
+        <v>1780.08</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1036-244-CM26</t>
+          <t>1078078-3547-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19198,47 +19198,43 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.897.437-3</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>154.85</v>
+        <v>7841.73</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1078078-3555-CM26</t>
+          <t>1036-244-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19258,32 +19254,32 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -19297,13 +19293,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>503.71</v>
+        <v>154.85</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1078078-3572-CM26</t>
+          <t>1078078-3555-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19318,7 +19314,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -19343,17 +19339,17 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -19362,13 +19358,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1252.22</v>
+        <v>503.71</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1078078-3565-CM26</t>
+          <t>1078078-3571-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19408,12 +19404,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -19423,13 +19419,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1960.51</v>
+        <v>431.5</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1078078-3566-CM26</t>
+          <t>1078078-3570-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19469,32 +19465,28 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>7386.6</v>
+        <v>888.0700000000001</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1078078-3567-CM26</t>
+          <t>1078078-3569-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19534,28 +19526,32 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr"/>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1574.03</v>
+        <v>8004.78</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1078078-3569-CM26</t>
+          <t>1078078-3565-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19595,32 +19591,28 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.029.126-9</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>8004.78</v>
+        <v>1960.51</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1078078-3570-CM26</t>
+          <t>1078078-3567-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19660,12 +19652,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19675,13 +19667,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>888.0700000000001</v>
+        <v>1574.03</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1078078-3571-CM26</t>
+          <t>1078078-3566-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19721,82 +19713,212 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>431.5</v>
+        <v>7386.6</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
+          <t>1078078-3572-CM26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>60.509.001-K</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>1252.22</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1078078-3568-CM26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>60.509.001-K</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>331.2</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
           <t>1078078-3573-CM26</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>60.509.001-K</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
         <is>
           <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
-      <c r="J310" t="inlineStr">
+      <c r="J312" t="inlineStr">
         <is>
           <t>70.016.130-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M310" s="2" t="n">
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="n">
         <v>7972.7</v>
       </c>
     </row>
